--- a/test_data/WTA/WTA Calculator - WHT Router/WTA Calculator - WHT Router_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Calculator - WHT Router/WTA Calculator - WHT Router_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WhtRouter_03</t>
+          <t>WhtRouter_05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'Source Jurisdiction' lists real countries</t>
+          <t>Completing Source/Income Stream/Residence and Calculate renders a results table</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Opening the 'Source Jurisdiction' select must list real country names (e.g. Australia, Bangladesh), not placeholder/empty options.</t>
+          <t>Completing Australia -&gt; Portfolio Dividend -&gt; Singapore and clicking Calculate must render a results table with Best Rate/Domestic Rate/Treaty Rate rows and a scenario heading reading 'Portfolio Dividend paid from Australia to Singapore'.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -653,29 +653,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Source: Australia, Stream: Portfolio Dividend, Residence: Singapore</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open WHT Router
-2. Open 'Source Jurisdiction'
-3. Verify real countries are listed</t>
+2. Complete Australia -&gt; Portfolio Dividend -&gt; Singapore, Calculate
+3. Verify the results table and scenario heading</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Opening the 'Source Jurisdiction' select must list real country names (e.g. Australia, Bangladesh), not placeholder/empty options.</t>
+          <t>Completing Australia -&gt; Portfolio Dividend -&gt; Singapore and clicking Calculate must render a results table with Best Rate/Domestic Rate/Treaty Rate rows and a scenario heading reading 'Portfolio Dividend paid from Australia to Singapore'.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>'Source Jurisdiction' correctly lists 120 real countries.</t>
+          <t>The results table rendered correctly with the expected scenario heading.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Source Jurisdiction' lists real countries including Australia</t>
+          <t>[PASS] Results table renders with the correct scenario heading</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WhtRouter_04</t>
+          <t>WhtRouter_06</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>'Income Stream' lists real income categories</t>
+          <t>Best/Domestic/Treaty Rate match the live WHT Router API</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Income Stream' must list real categories (Portfolio Dividend, Substantial Holding Dividend, General Interest payments, Patent/Trademark/Copyright Royalties, Lease payments, Technical Service Fees), confirmed live.</t>
+          <t>With Australia -&gt; Portfolio Dividend -&gt; Singapore selected, the UI's Best Rate/Domestic Rate/Treaty Rate must match an independent call to the live WHT_ROUTER_API - confirmed a public endpoint, not compared against itself.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -712,29 +712,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HostCountry=AU, TargetCountry=SG, Stream=Portfolio Dividend</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open WHT Router
-2. Open 'Income Stream'
-3. Verify the expected categories are present</t>
+          <t>1. Log in, open WHT Router, complete AU -&gt; Portfolio Dividend -&gt; SG
+2. Independently POST to the live WHT Router API with the same inputs
+3. Verify the UI's Best/Domestic/Treaty Rate match the API response</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Income Stream' must list real categories (Portfolio Dividend, Substantial Holding Dividend, General Interest payments, Patent/Trademark/Copyright Royalties, Lease payments, Technical Service Fees), confirmed live.</t>
+          <t>With Australia -&gt; Portfolio Dividend -&gt; Singapore selected, the UI's Best Rate/Domestic Rate/Treaty Rate must match an independent call to the live WHT_ROUTER_API - confirmed a public endpoint, not compared against itself.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>'Income Stream' correctly lists all expected categories.</t>
+          <t>The UI's rates (best=15%, domestic=30%, treaty=15%) correctly matched the independently-fetched live API values.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Income Stream' lists the expected real categories</t>
+          <t>[PASS] UI rates match the independently-fetched API values</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>WhtRouter_05</t>
+          <t>WhtRouter_09</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Completing Source/Income Stream/Residence and Calculate renders a results table</t>
+          <t>'Start over' shows a confirmation dialog</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Completing Australia -&gt; Portfolio Dividend -&gt; Singapore and clicking Calculate must render a results table with Best Rate/Domestic Rate/Treaty Rate rows and a scenario heading reading 'Portfolio Dividend paid from Australia to Singapore'.</t>
+          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions, not reset immediately.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -771,29 +771,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Source: Australia, Stream: Portfolio Dividend, Residence: Singapore</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open WHT Router
-2. Complete Australia -&gt; Portfolio Dividend -&gt; Singapore, Calculate
-3. Verify the results table and scenario heading</t>
+2. Click 'Start over'
+3. Verify the confirmation dialog</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Completing Australia -&gt; Portfolio Dividend -&gt; Singapore and clicking Calculate must render a results table with Best Rate/Domestic Rate/Treaty Rate rows and a scenario heading reading 'Portfolio Dividend paid from Australia to Singapore'.</t>
+          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions, not reset immediately.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>The results table rendered correctly with the expected scenario heading.</t>
+          <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Results table renders with the correct scenario heading</t>
+          <t>[PASS] 'Start over' shows the expected confirmation dialog</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>WhtRouter_06</t>
+          <t>WhtRouter_12</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Best/Domestic/Treaty Rate match the live WHT Router API</t>
+          <t>Switching to 'By Entity' swaps in Corporate Group/Company fields</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>With Australia -&gt; Portfolio Dividend -&gt; Singapore selected, the UI's Best Rate/Domestic Rate/Treaty Rate must match an independent call to the live WHT_ROUTER_API - confirmed a public endpoint, not compared against itself.</t>
+          <t>Clicking 'By Entity' must swap Source/Residence Jurisdiction selects for Corporate Group, Source Company and Residence Company fields.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,679 +830,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>HostCountry=AU, TargetCountry=SG, Stream=Portfolio Dividend</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, complete AU -&gt; Portfolio Dividend -&gt; SG
-2. Independently POST to the live WHT Router API with the same inputs
-3. Verify the UI's Best/Domestic/Treaty Rate match the API response</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia -&gt; Portfolio Dividend -&gt; Singapore selected, the UI's Best Rate/Domestic Rate/Treaty Rate must match an independent call to the live WHT_ROUTER_API - confirmed a public endpoint, not compared against itself.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>The UI's rates (best=15%, domestic=30%, treaty=15%) correctly matched the independently-fetched live API values.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] UI rates match the independently-fetched API values</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Generate Memo/Get Forms/Add to Project render once results are calculated</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>After a successful calculation, the 3 action buttons (Generate Memo, Get Forms, Add to Project) must be present and enabled.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, AU -&gt; Portfolio Dividend -&gt; SG calculated.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, complete AU -&gt; Portfolio Dividend -&gt; SG, Calculate
-2. Verify the 3 action buttons are visible and enabled</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>After a successful calculation, the 3 action buttons (Generate Memo, Get Forms, Add to Project) must be present and enabled.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>All 3 action buttons correctly appeared and were enabled after calculation.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 3 action buttons are visible and enabled after calculation</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Selecting the same country for both jurisdictions shows a blocking message</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia as both Source and Residence Jurisdiction must trigger a modal reading 'Please select different Source Jurisdiction and Residence Jurisdiction.' with only a Cancel action - confirmed live real validation, no API call fires.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Source: Australia, Residence: Australia</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, select Australia as Source
-2. Select Australia as Residence too
-3. Verify the blocking message modal</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia as both Source and Residence Jurisdiction must trigger a modal reading 'Please select different Source Jurisdiction and Residence Jurisdiction.' with only a Cancel action - confirmed live real validation, no API call fires.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Selecting the same country for both jurisdictions correctly triggered the real blocking validation message.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The same-jurisdiction validation modal shows the expected message with only Cancel</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' shows a confirmation dialog</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions, not reset immediately.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router
-2. Click 'Start over'
-3. Verify the confirmation dialog</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions, not reset immediately.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Start over' shows the expected confirmation dialog</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' Cancel keeps the current selections</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Clicking Cancel on the Start Over confirmation must leave the already-selected Source Jurisdiction untouched.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Source: Australia</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, select Australia as Source
-2. Click 'Start over' then Cancel
-3. Verify Source Jurisdiction is still Australia</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Clicking Cancel on the Start Over confirmation must leave the already-selected Source Jurisdiction untouched.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Cancelling 'Start over' correctly preserved the current selection.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Source Jurisdiction selection survives Cancel</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' Yes resets the selections back to placeholder state</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' (Yes) must reset the Source Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Source: Australia</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, select Australia as Source
-2. Click 'Start over' then Yes
-3. Verify Source Jurisdiction resets to 'Select'</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' (Yes) must reset the Source Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' correctly reset the selection to its placeholder state.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Source Jurisdiction resets to the 'Select' placeholder</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'By Entity' swaps in Corporate Group/Company fields</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'By Entity' must swap Source/Residence Jurisdiction selects for Corporate Group, Source Company and Residence Company fields.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open WHT Router
 2. Click 'By Entity'
 3. Verify 'Corporate Group' and 'Source Company' fields are now visible</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Clicking 'By Entity' must swap Source/Residence Jurisdiction selects for Corporate Group, Source Company and Residence Company fields.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Switching to 'By Entity' correctly swapped in the entity-based fields.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'By Entity' mode shows Corporate Group/Source Company fields</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' lists this account's real entity charts</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts (not placeholder/empty options).</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' mode selected.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, switch to 'By Entity'
-2. Open 'Corporate Group'
-3. Verify at least one real entity chart is listed</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts (not placeholder/empty options).</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' correctly lists 20 real entity chart(s): ['Demo Entity Chart', 'Natmed', 'Empty', 'N', 'Empty Entity Chart', 'Copy of Demo Import Test', 'New Chart with 3rd Party', 'Testing Empty Chart', 'New AG', 'New 3423', 'new', 'testt', 'Royal Enfield Incorporation', 'Test MM', 'new v2', 'Blank', 'JHUMKAH', 'RETRS', 'chuppp', 'BEINTEHA'].</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Corporate Group' lists at least one real entity chart</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Switching back to 'By Jurisdiction' restores jurisdiction-based fields</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>After switching to 'By Entity' and back to 'By Jurisdiction', the Source/Residence Jurisdiction selects must be visible again (not the entity fields).</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, switch to 'By Entity' then back to 'By Jurisdiction'
-2. Verify 'Source Jurisdiction' is visible again</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>After switching to 'By Entity' and back to 'By Jurisdiction', the Source/Residence Jurisdiction selects must be visible again (not the entity fields).</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Switching back to 'By Jurisdiction' correctly restored the jurisdiction-based fields.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Source Jurisdiction' select is visible after switching back</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>'Intermediaries 1' Select opens the Intermediate Streams/Jurisdictions modal</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Select' link under the optional 'Intermediaries 1' row must open a modal titled 'Intermediate Streams and Jurisdictions' with separate Streams and Countries checklists.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router
-2. Click 'Intermediaries 1' Select
-3. Verify the modal and both checklists are visible</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the 'Select' link under the optional 'Intermediaries 1' row must open a modal titled 'Intermediate Streams and Jurisdictions' with separate Streams and Countries checklists.</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>'Intermediaries 1' Select correctly opened the modal with its Streams/Countries checklists.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The Intermediate Streams/Jurisdictions modal opens with its controls visible</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_16</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>'Select All' checks every stream in the Intermediaries modal</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Select All' in the Streams column must check every stream checkbox, e.g. 'Portfolio Dividend'.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Intermediaries 1 modal open.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, open 'Intermediaries 1'
-2. Click 'Select All'
-3. Verify 'Portfolio Dividend' is checked</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Select All' in the Streams column must check every stream checkbox, e.g. 'Portfolio Dividend'.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>'Select All' correctly checked every stream, including 'Portfolio Dividend'.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Select All' checks the 'Portfolio Dividend' stream checkbox</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>WhtRouter_17</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - WHT Router</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>'Done' closes the Intermediaries modal</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Done' in the Intermediate Streams/Jurisdictions modal must close it and return to the main WHT Router form.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Intermediaries 1 modal open.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Router, open 'Intermediaries 1'
-2. Click 'Done'
-3. Verify the modal is closed</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Done' in the Intermediate Streams/Jurisdictions modal must close it and return to the main WHT Router form.</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>'Done' correctly closed the Intermediaries modal.</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The Intermediaries modal closes after 'Done'</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
